--- a/ig/DM-OCTOBRE-2024/CodeSystem-TRE-R66-CategorieEtablissement.xlsx
+++ b/ig/DM-OCTOBRE-2024/CodeSystem-TRE-R66-CategorieEtablissement.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="994" uniqueCount="677">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1009" uniqueCount="686">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20240927120000</t>
+    <t>20241025120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-27T12:00:00+01:00</t>
+    <t>2024-10-25T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -775,7 +775,13 @@
     <t>241</t>
   </si>
   <si>
-    <t>Foyer d'Action Educative (F.A.E.)</t>
+    <t>Établissement de Placement</t>
+  </si>
+  <si>
+    <t>242</t>
+  </si>
+  <si>
+    <t>Service d’Activité de Jour</t>
   </si>
   <si>
     <t>246</t>
@@ -1633,13 +1639,13 @@
     <t>440</t>
   </si>
   <si>
-    <t>Service Investigation Orientation Educative (S.I.O.E.)</t>
+    <t>Service d’Investigation Educative</t>
   </si>
   <si>
     <t>441</t>
   </si>
   <si>
-    <t>Centre d'Action Educative (C.A.E.)</t>
+    <t>Service d’Intervention Educative en Milieu Ouvert</t>
   </si>
   <si>
     <t>442</t>
@@ -1729,7 +1735,7 @@
     <t>462</t>
   </si>
   <si>
-    <t>Lieux de vie</t>
+    <t>Lieux de Vie et d’Accueil</t>
   </si>
   <si>
     <t>463</t>
@@ -1996,7 +2002,7 @@
     <t>646</t>
   </si>
   <si>
-    <t>Centre de vaccination international</t>
+    <t>Centre de Vaccination Internationale</t>
   </si>
   <si>
     <t>647</t>
@@ -2005,6 +2011,12 @@
     <t>Equipe de Soins Spécialisés</t>
   </si>
   <si>
+    <t>648</t>
+  </si>
+  <si>
+    <t>Structure qui contribue au Service d'Accès aux Soins</t>
+  </si>
+  <si>
     <t>690</t>
   </si>
   <si>
@@ -2045,6 +2057,21 @@
   </si>
   <si>
     <t>Maison sport-santé</t>
+  </si>
+  <si>
+    <t>Catégorie créée à la demande du ROR. A date aucun enregistrement n'est prévu dans FINESS pour cette catégorie</t>
+  </si>
+  <si>
+    <t>701</t>
+  </si>
+  <si>
+    <t>Maison des adolescents (MDA)</t>
+  </si>
+  <si>
+    <t>702</t>
+  </si>
+  <si>
+    <t>Point Accueil Ecoute Jeunes (PAEJ)</t>
   </si>
 </sst>
 </file>
@@ -2418,7 +2445,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D314"/>
+  <dimension ref="A1:D318"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -5673,21 +5700,21 @@
       <c r="C271" t="s" s="2">
         <v>589</v>
       </c>
-      <c r="D271" t="s" s="2">
-        <v>590</v>
-      </c>
+      <c r="D271" s="2"/>
     </row>
     <row r="272">
       <c r="A272" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B272" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="C272" t="s" s="2">
         <v>591</v>
       </c>
-      <c r="C272" t="s" s="2">
+      <c r="D272" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="D272" s="2"/>
     </row>
     <row r="273">
       <c r="A273" t="s" s="2">
@@ -6192,6 +6219,60 @@
         <v>676</v>
       </c>
       <c r="D314" s="2"/>
+    </row>
+    <row r="315">
+      <c r="A315" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B315" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="C315" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="D315" s="2"/>
+    </row>
+    <row r="316">
+      <c r="A316" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B316" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="C316" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="D316" t="s" s="2">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B317" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="C317" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="D317" t="s" s="2">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B318" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="C318" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="D318" t="s" s="2">
+        <v>681</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
